--- a/datos_ciliopatias/Anexo3.xlsx
+++ b/datos_ciliopatias/Anexo3.xlsx
@@ -1,101 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\TFM\TFM_R_proyect\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE54864-6149-491A-89B0-3B4B5A6CB88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>eigenvalues</t>
-  </si>
-  <si>
-    <t>porcentaje varianza</t>
-  </si>
-  <si>
-    <t>varianza acumulada</t>
-  </si>
-  <si>
-    <t>Dim.1</t>
-  </si>
-  <si>
-    <t>Dim.2</t>
-  </si>
-  <si>
-    <t>Dim.3</t>
-  </si>
-  <si>
-    <t>Dim.4</t>
-  </si>
-  <si>
-    <t>Dim.5</t>
-  </si>
-  <si>
-    <t>Dim.6</t>
-  </si>
-  <si>
-    <t>Dim.7</t>
-  </si>
-  <si>
-    <t>Dim.8</t>
-  </si>
-  <si>
-    <t>Dim.9</t>
-  </si>
-  <si>
-    <t>Dim.10</t>
-  </si>
-  <si>
-    <t>Dim.11</t>
-  </si>
-  <si>
-    <t>Dim.12</t>
-  </si>
-  <si>
-    <t>Dim.13</t>
-  </si>
-  <si>
-    <t>Dim.14</t>
-  </si>
-  <si>
-    <t>Dim.15</t>
-  </si>
-  <si>
-    <t>Dim.16</t>
-  </si>
-  <si>
-    <t>Dim.17</t>
-  </si>
-  <si>
-    <t>Dim.18</t>
-  </si>
-  <si>
-    <t>Dim.19</t>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eigenvalues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porcentaje varianza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">varianza acumulada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim.19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -131,15 +124,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,15 +405,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,274 +423,274 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>3.93761305692757</v>
       </c>
-      <c r="C2">
-        <v>20.724279246987201</v>
-      </c>
-      <c r="D2">
-        <v>20.724279246987201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C2" t="n">
+        <v>20.7242792469872</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.7242792469872</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>3.5963256170126701</v>
-      </c>
-      <c r="C3">
-        <v>18.928029563224602</v>
-      </c>
-      <c r="D3">
+      <c r="B3" t="n">
+        <v>3.59632561701267</v>
+      </c>
+      <c r="C3" t="n">
+        <v>18.9280295632246</v>
+      </c>
+      <c r="D3" t="n">
         <v>39.6523088102118</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2.34424755656734</v>
       </c>
-      <c r="C4">
-        <v>12.338145034564899</v>
-      </c>
-      <c r="D4">
-        <v>51.990453844776702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="n">
+        <v>12.3381450345649</v>
+      </c>
+      <c r="D4" t="n">
+        <v>51.9904538447767</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>1.89912036816412</v>
       </c>
-      <c r="C5">
-        <v>9.9953703587585192</v>
-      </c>
-      <c r="D5">
-        <v>61.985824203535202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="n">
+        <v>9.99537035875852</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61.9858242035352</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1.20916033607956</v>
       </c>
-      <c r="C6">
-        <v>6.3640017688397998</v>
-      </c>
-      <c r="D6">
-        <v>68.349825972375001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="n">
+        <v>6.3640017688398</v>
+      </c>
+      <c r="D6" t="n">
+        <v>68.349825972375</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1.11841064311317</v>
       </c>
-      <c r="C7">
-        <v>5.8863718058587704</v>
-      </c>
-      <c r="D7">
-        <v>74.236197778233802</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="n">
+        <v>5.88637180585877</v>
+      </c>
+      <c r="D7" t="n">
+        <v>74.2361977782338</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1.07121079387072</v>
       </c>
-      <c r="C8">
-        <v>5.6379515466880097</v>
-      </c>
-      <c r="D8">
-        <v>79.874149324921802</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="n">
+        <v>5.63795154668801</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79.8741493249218</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>0.77880561160971895</v>
-      </c>
-      <c r="C9">
-        <v>4.0989769032090502</v>
-      </c>
-      <c r="D9">
-        <v>83.973126228130894</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="n">
+        <v>0.778805611609719</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.09897690320905</v>
+      </c>
+      <c r="D9" t="n">
+        <v>83.9731262281309</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>0.64121977084229598</v>
-      </c>
-      <c r="C10">
-        <v>3.3748408991699801</v>
-      </c>
-      <c r="D10">
-        <v>87.347967127300805</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="n">
+        <v>0.641219770842296</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.37484089916998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87.3479671273008</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <v>0.54514461322961405</v>
-      </c>
-      <c r="C11">
-        <v>2.8691821748927002</v>
-      </c>
-      <c r="D11">
-        <v>90.217149302193604</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="n">
+        <v>0.545144613229614</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.8691821748927</v>
+      </c>
+      <c r="D11" t="n">
+        <v>90.2171493021936</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
-        <v>0.43878271438202598</v>
-      </c>
-      <c r="C12">
-        <v>2.3093827072738198</v>
-      </c>
-      <c r="D12">
-        <v>92.526532009467402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="n">
+        <v>0.438782714382026</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.30938270727382</v>
+      </c>
+      <c r="D12" t="n">
+        <v>92.5265320094674</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>0.32119722052050298</v>
-      </c>
-      <c r="C13">
-        <v>1.6905116869500201</v>
-      </c>
-      <c r="D13">
-        <v>94.217043696417406</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="n">
+        <v>0.321197220520503</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.69051168695002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>94.2170436964174</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
-        <v>0.30414595686086499</v>
-      </c>
-      <c r="C14">
-        <v>1.6007681940045499</v>
-      </c>
-      <c r="D14">
-        <v>95.817811890422007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="n">
+        <v>0.304145956860865</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.60076819400455</v>
+      </c>
+      <c r="D14" t="n">
+        <v>95.817811890422</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>0.202126723295634</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1.06382485945071</v>
       </c>
-      <c r="D15">
-        <v>96.881636749872698</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D15" t="n">
+        <v>96.8816367498727</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>0.170649172381661</v>
       </c>
-      <c r="C16">
-        <v>0.89815353885084903</v>
-      </c>
-      <c r="D16">
-        <v>97.779790288723504</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C16" t="n">
+        <v>0.898153538850849</v>
+      </c>
+      <c r="D16" t="n">
+        <v>97.7797902887235</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>0.13772438553274</v>
       </c>
-      <c r="C17">
-        <v>0.72486518701442204</v>
-      </c>
-      <c r="D17">
-        <v>98.504655475737906</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="n">
+        <v>0.724865187014422</v>
+      </c>
+      <c r="D17" t="n">
+        <v>98.5046554757379</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
-        <v>0.12957179082491199</v>
-      </c>
-      <c r="C18">
-        <v>0.68195679381532703</v>
-      </c>
-      <c r="D18">
-        <v>99.186612269553294</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="n">
+        <v>0.129571790824912</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.681956793815327</v>
+      </c>
+      <c r="D18" t="n">
+        <v>99.1866122695533</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
-        <v>8.7410645495242106E-2</v>
-      </c>
-      <c r="C19">
+      <c r="B19" t="n">
+        <v>0.0874106454952421</v>
+      </c>
+      <c r="C19" t="n">
         <v>0.460056028922327</v>
       </c>
-      <c r="D19">
-        <v>99.646668298475603</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" t="n">
+        <v>99.6466682984756</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>6.7133023289640603E-2</v>
-      </c>
-      <c r="C20">
+      <c r="B20" t="n">
+        <v>0.0671330232896406</v>
+      </c>
+      <c r="C20" t="n">
         <v>0.353331701524424</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>